--- a/public/i18n-config.xlsx
+++ b/public/i18n-config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\个人项目测试\yutu-imooc\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D579293-9696-4F76-B93A-B0B02D8B3943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE196FE1-8D1A-427A-BFE4-5EC67E2DDF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
   <si>
     <t>keyPath</t>
   </si>
@@ -359,6 +359,18 @@
   </si>
   <si>
     <t>vs same period last year</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中西区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Central and Western District</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>card.one</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
@@ -1138,6 +1150,17 @@
         <v>102</v>
       </c>
     </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
